--- a/output/graficos_nacionales/plot_nacional_s_isapre_a_2023.xlsx
+++ b/output/graficos_nacionales/plot_nacional_s_isapre_a_2023.xlsx
@@ -15451,7 +15451,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Afiliación ISAPRE</t>
+          <t>Por comunas</t>
         </is>
       </c>
     </row>

--- a/output/graficos_nacionales/plot_nacional_s_isapre_a_2023.xlsx
+++ b/output/graficos_nacionales/plot_nacional_s_isapre_a_2023.xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2762,7 +2762,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3682,7 +3682,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3820,7 +3820,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -3958,7 +3958,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4280,7 +4280,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -5384,7 +5384,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -5752,7 +5752,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -5936,7 +5936,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -6304,7 +6304,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -6626,7 +6626,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -6764,7 +6764,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -6994,7 +6994,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -7178,7 +7178,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -7500,7 +7500,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -7546,7 +7546,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -7592,7 +7592,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -7822,7 +7822,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -7868,7 +7868,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -8006,7 +8006,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -8190,7 +8190,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -8236,7 +8236,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -8420,7 +8420,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -8512,7 +8512,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -8604,7 +8604,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -8650,7 +8650,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -9524,7 +9524,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -9708,7 +9708,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -9754,7 +9754,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -10122,7 +10122,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -10490,7 +10490,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -10582,7 +10582,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -10628,7 +10628,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -10674,7 +10674,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -10720,7 +10720,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -10766,7 +10766,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -10950,7 +10950,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -11134,7 +11134,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -11226,7 +11226,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -11318,7 +11318,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -11410,7 +11410,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -11502,7 +11502,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -11594,7 +11594,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -11686,7 +11686,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -11916,7 +11916,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -12008,7 +12008,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -12192,7 +12192,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -12284,7 +12284,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -12422,7 +12422,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -12468,7 +12468,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -12514,7 +12514,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -12560,7 +12560,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -12606,7 +12606,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -12652,7 +12652,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -12790,7 +12790,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -12836,7 +12836,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -12882,7 +12882,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -12928,7 +12928,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -13020,7 +13020,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -13066,7 +13066,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -13158,7 +13158,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -13204,7 +13204,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -13250,7 +13250,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -13296,7 +13296,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -13342,7 +13342,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -13480,7 +13480,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -13756,7 +13756,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -13802,7 +13802,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -13848,7 +13848,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -13894,7 +13894,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -13986,7 +13986,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -14032,7 +14032,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -14078,7 +14078,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -14124,7 +14124,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -14170,7 +14170,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -14262,7 +14262,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -14354,7 +14354,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -14400,7 +14400,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -14446,7 +14446,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -14492,7 +14492,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -14538,7 +14538,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -14584,7 +14584,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -14630,7 +14630,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -14676,7 +14676,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -14722,7 +14722,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -14768,7 +14768,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -14814,7 +14814,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -14860,7 +14860,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -14906,7 +14906,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -14998,7 +14998,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -15044,7 +15044,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -15090,7 +15090,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -15136,7 +15136,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -15182,7 +15182,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -15228,7 +15228,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -15320,7 +15320,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -15366,7 +15366,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">

--- a/output/graficos_nacionales/plot_nacional_s_isapre_a_2023.xlsx
+++ b/output/graficos_nacionales/plot_nacional_s_isapre_a_2023.xlsx
@@ -2074,7 +2074,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-30 15:55</t>
+    <t xml:space="preserve">2026-08-28 15:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_s_isapre_a_2023.xlsx
+++ b/output/graficos_nacionales/plot_nacional_s_isapre_a_2023.xlsx
@@ -2074,7 +2074,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-28 15:12</t>
+    <t xml:space="preserve">2026-08-29 05:48</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_s_isapre_a_2023.xlsx
+++ b/output/graficos_nacionales/plot_nacional_s_isapre_a_2023.xlsx
@@ -2074,7 +2074,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-29 05:48</t>
+    <t xml:space="preserve">2026-09-07 13:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_s_isapre_a_2023.xlsx
+++ b/output/graficos_nacionales/plot_nacional_s_isapre_a_2023.xlsx
@@ -2074,7 +2074,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 13:10</t>
+    <t xml:space="preserve">2026-09-08 10:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
